--- a/outputs/llm_eval/topical_yjx/sig/Critic_correlation_results.xlsx
+++ b/outputs/llm_eval/topical_yjx/sig/Critic_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.2767574208676066</v>
+        <v>0.4449459252382799</v>
       </c>
       <c r="C2">
-        <v>0.2869637164720277</v>
+        <v>0.4425717444569408</v>
       </c>
       <c r="D2">
-        <v>0.2281026244134517</v>
+        <v>0.3845284075019733</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.2455812520037871</v>
+        <v>0.4382106974175602</v>
       </c>
       <c r="C3">
-        <v>0.2566315092662969</v>
+        <v>0.4254588839197343</v>
       </c>
       <c r="D3">
-        <v>0.211355358806559</v>
+        <v>0.4025794872036992</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,18 +445,27 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.4712226156579189</v>
+        <v>0.6000565543483248</v>
       </c>
       <c r="C4">
-        <v>0.4876855600952255</v>
+        <v>0.5970720512313704</v>
       </c>
       <c r="D4">
-        <v>0.4064606594547922</v>
+        <v>0.5529242596521021</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
+      </c>
+      <c r="B5">
+        <v>0.5055036447963634</v>
+      </c>
+      <c r="C5">
+        <v>0.5131390739251324</v>
+      </c>
+      <c r="D5">
+        <v>0.4918375570451935</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/llm_eval/topical_yjx/sig/Critic_correlation_results.xlsx
+++ b/outputs/llm_eval/topical_yjx/sig/Critic_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.4449459252382799</v>
+        <v>0.4809102303971516</v>
       </c>
       <c r="C2">
-        <v>0.4425717444569408</v>
+        <v>0.461518281406711</v>
       </c>
       <c r="D2">
-        <v>0.3845284075019733</v>
+        <v>0.4246423304583332</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.4382106974175602</v>
+        <v>0.478581146265558</v>
       </c>
       <c r="C3">
-        <v>0.4254588839197343</v>
+        <v>0.4660205460870653</v>
       </c>
       <c r="D3">
-        <v>0.4025794872036992</v>
+        <v>0.4327143046522233</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,13 +445,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.6000565543483248</v>
+        <v>0.5987471318617911</v>
       </c>
       <c r="C4">
-        <v>0.5970720512313704</v>
+        <v>0.6017192784840911</v>
       </c>
       <c r="D4">
-        <v>0.5529242596521021</v>
+        <v>0.5482156876464754</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -459,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.5055036447963634</v>
+        <v>0.5461546561182427</v>
       </c>
       <c r="C5">
-        <v>0.5131390739251324</v>
+        <v>0.5604113096395354</v>
       </c>
       <c r="D5">
-        <v>0.4918375570451935</v>
+        <v>0.5278428729520274</v>
       </c>
     </row>
   </sheetData>
